--- a/artfynd/S 1118-2023 artfynd.xlsx
+++ b/artfynd/S 1118-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -776,27 +776,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119010103</v>
+        <v>135474291</v>
       </c>
       <c r="B3" t="n">
-        <v>58636</v>
+        <v>57975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -809,19 +809,31 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Över_grucken_Stensjön, Hjd</t>
+          <t>Stensjön, Över-Grucken, Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416439</v>
+        <v>416037</v>
       </c>
       <c r="R3" t="n">
-        <v>6966770</v>
+        <v>6966866</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -845,22 +857,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>06:38</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>06:38</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,19 +877,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Stefan Dahlsten</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Stefan Dahlsten</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119010108</v>
+        <v>119010103</v>
       </c>
       <c r="B4" t="n">
         <v>58636</v>
@@ -926,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416871</v>
+        <v>416439</v>
       </c>
       <c r="R4" t="n">
-        <v>6966878</v>
+        <v>6966770</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -961,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -971,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,7 +1000,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119010111</v>
+        <v>119010108</v>
       </c>
       <c r="B5" t="n">
         <v>58636</v>
@@ -1037,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416496</v>
+        <v>416871</v>
       </c>
       <c r="R5" t="n">
-        <v>6966999</v>
+        <v>6966878</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1072,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1082,7 +1084,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,6 +1108,117 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>119010111</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Över_grucken_Stensjön, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>416496</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6966999</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/S 1118-2023 artfynd.xlsx
+++ b/artfynd/S 1118-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87046870</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135474291</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119010103</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119010108</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1219,8 +1244,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119010111</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 1118-2023 artfynd.xlsx
+++ b/artfynd/S 1118-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135474291</v>
       </c>
       <c r="B3" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 1118-2023 artfynd.xlsx
+++ b/artfynd/S 1118-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,27 +786,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119010103</v>
+        <v>135474291</v>
       </c>
       <c r="B3" t="n">
-        <v>58636</v>
+        <v>57980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -819,19 +819,31 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Över_grucken_Stensjön, Hjd</t>
+          <t>Stensjön, Över-Grucken, Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416439</v>
+        <v>416037</v>
       </c>
       <c r="R3" t="n">
-        <v>6966770</v>
+        <v>6966866</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,22 +867,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>06:38</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>06:38</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,24 +887,24 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Stefan Dahlsten</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Stefan Dahlsten</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119010103</t>
+          <t>https://artportalen.se/Sighting/135474291</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119010108</v>
+        <v>119010103</v>
       </c>
       <c r="B4" t="n">
         <v>58636</v>
@@ -941,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416871</v>
+        <v>416439</v>
       </c>
       <c r="R4" t="n">
-        <v>6966878</v>
+        <v>6966770</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,13 +1014,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119010108</t>
+          <t>https://artportalen.se/Sighting/119010103</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119010111</v>
+        <v>119010108</v>
       </c>
       <c r="B5" t="n">
         <v>58636</v>
@@ -1057,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416496</v>
+        <v>416871</v>
       </c>
       <c r="R5" t="n">
-        <v>6966999</v>
+        <v>6966878</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1092,7 +1094,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1102,7 +1104,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,6 +1129,122 @@
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119010108</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>119010111</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Över_grucken_Stensjön, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>416496</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6966999</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/119010111</t>
         </is>
@@ -1138,6 +1256,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1118-2023 artfynd.xlsx
+++ b/artfynd/S 1118-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,27 +786,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135474291</v>
+        <v>119010103</v>
       </c>
       <c r="B3" t="n">
-        <v>57980</v>
+        <v>58636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -819,31 +819,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stensjön, Över-Grucken, Storsjö, Hjd</t>
+          <t>Över_grucken_Stensjön, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416037</v>
+        <v>416439</v>
       </c>
       <c r="R3" t="n">
-        <v>6966866</v>
+        <v>6966770</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,12 +855,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,24 +885,24 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Stefan Dahlsten</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stefan Dahlsten</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135474291</t>
+          <t>https://artportalen.se/Sighting/119010103</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119010103</v>
+        <v>119010108</v>
       </c>
       <c r="B4" t="n">
         <v>58636</v>
@@ -943,13 +941,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416439</v>
+        <v>416871</v>
       </c>
       <c r="R4" t="n">
-        <v>6966770</v>
+        <v>6966878</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +976,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +986,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,13 +1012,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119010103</t>
+          <t>https://artportalen.se/Sighting/119010108</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119010108</v>
+        <v>119010111</v>
       </c>
       <c r="B5" t="n">
         <v>58636</v>
@@ -1059,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416871</v>
+        <v>416496</v>
       </c>
       <c r="R5" t="n">
-        <v>6966878</v>
+        <v>6966999</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1094,7 +1092,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1104,7 +1102,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,122 +1127,6 @@
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/119010108</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>119010111</v>
-      </c>
-      <c r="B6" t="n">
-        <v>58636</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>103044</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Grönsiska</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Spinus spinus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Över_grucken_Stensjön, Hjd</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>416496</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6966999</v>
-      </c>
-      <c r="S6" t="n">
-        <v>50</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2024-05-22</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>05:49</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2024-05-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>05:49</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/119010111</t>
         </is>
@@ -1256,7 +1138,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1118-2023 artfynd.xlsx
+++ b/artfynd/S 1118-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135474291</v>
       </c>
       <c r="B3" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 1118-2023 artfynd.xlsx
+++ b/artfynd/S 1118-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,27 +786,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135474291</v>
+        <v>119010103</v>
       </c>
       <c r="B3" t="n">
-        <v>57982</v>
+        <v>58636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -819,31 +819,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stensjön, Över-Grucken, Storsjö, Hjd</t>
+          <t>Över_grucken_Stensjön, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416037</v>
+        <v>416439</v>
       </c>
       <c r="R3" t="n">
-        <v>6966866</v>
+        <v>6966770</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,12 +855,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,24 +885,24 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Stefan Dahlsten</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stefan Dahlsten</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135474291</t>
+          <t>https://artportalen.se/Sighting/119010103</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119010103</v>
+        <v>119010108</v>
       </c>
       <c r="B4" t="n">
         <v>58636</v>
@@ -943,13 +941,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416439</v>
+        <v>416871</v>
       </c>
       <c r="R4" t="n">
-        <v>6966770</v>
+        <v>6966878</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +976,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +986,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,13 +1012,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119010103</t>
+          <t>https://artportalen.se/Sighting/119010108</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119010108</v>
+        <v>119010111</v>
       </c>
       <c r="B5" t="n">
         <v>58636</v>
@@ -1059,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416871</v>
+        <v>416496</v>
       </c>
       <c r="R5" t="n">
-        <v>6966878</v>
+        <v>6966999</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1094,7 +1092,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1104,7 +1102,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,122 +1127,6 @@
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/119010108</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>119010111</v>
-      </c>
-      <c r="B6" t="n">
-        <v>58636</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>103044</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Grönsiska</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Spinus spinus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Över_grucken_Stensjön, Hjd</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>416496</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6966999</v>
-      </c>
-      <c r="S6" t="n">
-        <v>50</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2024-05-22</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>05:49</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2024-05-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>05:49</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/119010111</t>
         </is>
@@ -1256,7 +1138,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1118-2023 artfynd.xlsx
+++ b/artfynd/S 1118-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,27 +786,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119010103</v>
+        <v>135474291</v>
       </c>
       <c r="B3" t="n">
-        <v>58636</v>
+        <v>57982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -819,19 +819,31 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Över_grucken_Stensjön, Hjd</t>
+          <t>Stensjön, Över-Grucken, Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416439</v>
+        <v>416037</v>
       </c>
       <c r="R3" t="n">
-        <v>6966770</v>
+        <v>6966866</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,22 +867,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>06:38</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>06:38</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,24 +887,24 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Stefan Dahlsten</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Stefan Dahlsten</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119010103</t>
+          <t>https://artportalen.se/Sighting/135474291</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119010108</v>
+        <v>119010103</v>
       </c>
       <c r="B4" t="n">
         <v>58636</v>
@@ -941,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416871</v>
+        <v>416439</v>
       </c>
       <c r="R4" t="n">
-        <v>6966878</v>
+        <v>6966770</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,13 +1014,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119010108</t>
+          <t>https://artportalen.se/Sighting/119010103</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119010111</v>
+        <v>119010108</v>
       </c>
       <c r="B5" t="n">
         <v>58636</v>
@@ -1057,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416496</v>
+        <v>416871</v>
       </c>
       <c r="R5" t="n">
-        <v>6966999</v>
+        <v>6966878</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1092,7 +1094,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1102,7 +1104,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,6 +1129,122 @@
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119010108</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>119010111</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Över_grucken_Stensjön, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>416496</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6966999</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/119010111</t>
         </is>
@@ -1138,6 +1256,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1118-2023 artfynd.xlsx
+++ b/artfynd/S 1118-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135474291</v>
       </c>
       <c r="B3" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 1118-2023 artfynd.xlsx
+++ b/artfynd/S 1118-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135474291</v>
       </c>
       <c r="B3" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 1118-2023 artfynd.xlsx
+++ b/artfynd/S 1118-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135474291</v>
       </c>
       <c r="B3" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 1118-2023 artfynd.xlsx
+++ b/artfynd/S 1118-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135474291</v>
       </c>
       <c r="B3" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 1118-2023 artfynd.xlsx
+++ b/artfynd/S 1118-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,27 +786,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135474291</v>
+        <v>119010103</v>
       </c>
       <c r="B3" t="n">
-        <v>57993</v>
+        <v>58636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -819,31 +819,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stensjön, Över-Grucken, Storsjö, Hjd</t>
+          <t>Över_grucken_Stensjön, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416037</v>
+        <v>416439</v>
       </c>
       <c r="R3" t="n">
-        <v>6966866</v>
+        <v>6966770</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,12 +855,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,24 +885,24 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Stefan Dahlsten</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stefan Dahlsten</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135474291</t>
+          <t>https://artportalen.se/Sighting/119010103</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119010103</v>
+        <v>119010108</v>
       </c>
       <c r="B4" t="n">
         <v>58636</v>
@@ -943,13 +941,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416439</v>
+        <v>416871</v>
       </c>
       <c r="R4" t="n">
-        <v>6966770</v>
+        <v>6966878</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +976,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +986,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,13 +1012,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119010103</t>
+          <t>https://artportalen.se/Sighting/119010108</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119010108</v>
+        <v>119010111</v>
       </c>
       <c r="B5" t="n">
         <v>58636</v>
@@ -1059,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416871</v>
+        <v>416496</v>
       </c>
       <c r="R5" t="n">
-        <v>6966878</v>
+        <v>6966999</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1094,7 +1092,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1104,7 +1102,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,122 +1127,6 @@
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/119010108</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>119010111</v>
-      </c>
-      <c r="B6" t="n">
-        <v>58636</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>103044</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Grönsiska</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Spinus spinus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Över_grucken_Stensjön, Hjd</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>416496</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6966999</v>
-      </c>
-      <c r="S6" t="n">
-        <v>50</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2024-05-22</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>05:49</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2024-05-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>05:49</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/119010111</t>
         </is>
@@ -1256,7 +1138,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1118-2023 artfynd.xlsx
+++ b/artfynd/S 1118-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,27 +786,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119010103</v>
+        <v>135474291</v>
       </c>
       <c r="B3" t="n">
-        <v>58636</v>
+        <v>58006</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -819,19 +819,31 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Över_grucken_Stensjön, Hjd</t>
+          <t>Stensjön, Över-Grucken, Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416439</v>
+        <v>416037</v>
       </c>
       <c r="R3" t="n">
-        <v>6966770</v>
+        <v>6966866</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,22 +867,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>06:38</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>06:38</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,24 +887,24 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Stefan Dahlsten</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Stefan Dahlsten</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119010103</t>
+          <t>https://artportalen.se/Sighting/135474291</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119010108</v>
+        <v>119010103</v>
       </c>
       <c r="B4" t="n">
         <v>58636</v>
@@ -941,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416871</v>
+        <v>416439</v>
       </c>
       <c r="R4" t="n">
-        <v>6966878</v>
+        <v>6966770</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,13 +1014,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119010108</t>
+          <t>https://artportalen.se/Sighting/119010103</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119010111</v>
+        <v>119010108</v>
       </c>
       <c r="B5" t="n">
         <v>58636</v>
@@ -1057,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416496</v>
+        <v>416871</v>
       </c>
       <c r="R5" t="n">
-        <v>6966999</v>
+        <v>6966878</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1092,7 +1094,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1102,7 +1104,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,6 +1129,122 @@
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119010108</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>119010111</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Över_grucken_Stensjön, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>416496</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6966999</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/119010111</t>
         </is>
@@ -1138,6 +1256,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
